--- a/src/results_template/CEC2017/50Dim.xlsx
+++ b/src/results_template/CEC2017/50Dim.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\Base-Optimization-Framework\src\results_template\CEC2017\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\src\results_template\CEC2017\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B217DA18-BDC2-453F-982D-088A92719D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AE0CBF-EBE3-4356-BD33-3684C6A24A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,20 +22,8 @@
     <sheet name="Friedman" sheetId="7" r:id="rId7"/>
     <sheet name="Explanation" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -44,12 +32,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="121">
   <si>
     <t>Comparison of optimization results for the CEC benchmark functions 2017 (50 Dim)</t>
   </si>
   <si>
     <t>Functions</t>
+  </si>
+  <si>
+    <t>Algorithm 1</t>
+  </si>
+  <si>
+    <t>Algorithm 2</t>
+  </si>
+  <si>
+    <t>Algorithm 3</t>
+  </si>
+  <si>
+    <t>Algorithm 4</t>
+  </si>
+  <si>
+    <t>Algorithm 5</t>
+  </si>
+  <si>
+    <t>Algorithm 6</t>
+  </si>
+  <si>
+    <t>Algorithm 7</t>
+  </si>
+  <si>
+    <t>Algorithm 8</t>
+  </si>
+  <si>
+    <t>Algorithm 9</t>
+  </si>
+  <si>
+    <t>Algorithm 10</t>
+  </si>
+  <si>
+    <t>Algorithm 11</t>
+  </si>
+  <si>
+    <t>Algorithm 12</t>
+  </si>
+  <si>
+    <t>Algorithm 13</t>
+  </si>
+  <si>
+    <t>Algorithm 14</t>
+  </si>
+  <si>
+    <t>Algorithm 15</t>
   </si>
   <si>
     <t>Unimodal
@@ -168,177 +201,129 @@
     <t>F30</t>
   </si>
   <si>
-    <t>Algorithm 1</t>
-  </si>
-  <si>
-    <t>Algorithm 2</t>
-  </si>
-  <si>
-    <t>Algorithm 3</t>
-  </si>
-  <si>
-    <t>Algorithm 4</t>
-  </si>
-  <si>
-    <t>Algorithm 5</t>
-  </si>
-  <si>
-    <t>Algorithm 6</t>
-  </si>
-  <si>
-    <t>Algorithm 7</t>
-  </si>
-  <si>
-    <t>Algorithm 8</t>
-  </si>
-  <si>
-    <t>Algorithm 9</t>
-  </si>
-  <si>
-    <t>Algorithm 10</t>
-  </si>
-  <si>
-    <t>Algorithm 11</t>
-  </si>
-  <si>
-    <t>Algorithm 12</t>
-  </si>
-  <si>
-    <t>Algorithm 13</t>
-  </si>
-  <si>
-    <t>Algorithm 14</t>
-  </si>
-  <si>
-    <t>Algorithm 15</t>
-  </si>
-  <si>
-    <t>Number of Best Functions</t>
+    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2017 (50 Dim)</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>alg_base vs alg2</t>
+  </si>
+  <si>
+    <t>alg_base vs alg3</t>
+  </si>
+  <si>
+    <t>alg_base vs alg4</t>
+  </si>
+  <si>
+    <t>alg_base vs alg5</t>
+  </si>
+  <si>
+    <t>alg_base vs alg6</t>
+  </si>
+  <si>
+    <t>alg_base vs alg7</t>
+  </si>
+  <si>
+    <t>alg_base vs alg8</t>
+  </si>
+  <si>
+    <t>alg_base vs alg9</t>
+  </si>
+  <si>
+    <t>alg_base vs alg10</t>
+  </si>
+  <si>
+    <t>alg_base vs alg11</t>
+  </si>
+  <si>
+    <t>alg_base vs alg12</t>
+  </si>
+  <si>
+    <t>alg_base vs alg13</t>
+  </si>
+  <si>
+    <t>alg_base vs alg14</t>
+  </si>
+  <si>
+    <t>alg_base vs alg15</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2017 (50 Dim)</t>
+  </si>
+  <si>
+    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2017 (50 Dim)</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2017 (50 Dim)</t>
+  </si>
+  <si>
+    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2017 (50 Dim)</t>
+  </si>
+  <si>
+    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2017 (50 Dim)</t>
+  </si>
+  <si>
+    <t>Algorithm 1 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 2 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 3 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 4 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 5 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 6 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 7 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 8 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 9 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 10 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 11 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 12 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 13 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 14 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 15 Rank</t>
+  </si>
+  <si>
+    <t>Best Algorithm</t>
+  </si>
+  <si>
+    <t>Kruskal-Wallis p</t>
+  </si>
+  <si>
+    <t>Significant?</t>
+  </si>
+  <si>
+    <t>Average Rank</t>
   </si>
   <si>
     <t>Overall Rank</t>
   </si>
   <si>
-    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2017 (50 Dim)</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>alg_base vs alg2</t>
-  </si>
-  <si>
-    <t>alg_base vs alg3</t>
-  </si>
-  <si>
-    <t>alg_base vs alg4</t>
-  </si>
-  <si>
-    <t>alg_base vs alg5</t>
-  </si>
-  <si>
-    <t>alg_base vs alg6</t>
-  </si>
-  <si>
-    <t>alg_base vs alg7</t>
-  </si>
-  <si>
-    <t>alg_base vs alg8</t>
-  </si>
-  <si>
-    <t>alg_base vs alg9</t>
-  </si>
-  <si>
-    <t>alg_base vs alg10</t>
-  </si>
-  <si>
-    <t>alg_base vs alg11</t>
-  </si>
-  <si>
-    <t>alg_base vs alg12</t>
-  </si>
-  <si>
-    <t>alg_base vs alg13</t>
-  </si>
-  <si>
-    <t>alg_base vs alg14</t>
-  </si>
-  <si>
-    <t>alg_base vs alg15</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2017 (50 Dim)</t>
-  </si>
-  <si>
-    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2017 (50 Dim)</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2017 (50 Dim)</t>
-  </si>
-  <si>
-    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2017 (50 Dim)</t>
-  </si>
-  <si>
-    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2017 (50 Dim)</t>
-  </si>
-  <si>
-    <t>Algorithm 1 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 2 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 3 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 4 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 5 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 6 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 7 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 8 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 9 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 10 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 11 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 12 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 13 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 14 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 15 Rank</t>
-  </si>
-  <si>
-    <t>Best Algorithm</t>
-  </si>
-  <si>
-    <t>Kruskal-Wallis p</t>
-  </si>
-  <si>
-    <t>Significant?</t>
-  </si>
-  <si>
-    <t>Average Rank</t>
-  </si>
-  <si>
     <t>Overall Friedman Test</t>
   </si>
   <si>
@@ -409,6 +394,12 @@
   </si>
   <si>
     <t>Optional figures showing the distribution of final objective values across independent runs for each function and algorithm.</t>
+  </si>
+  <si>
+    <t>Total number of best answers</t>
+  </si>
+  <si>
+    <t>Total number of equal-best answers</t>
   </si>
 </sst>
 </file>
@@ -534,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -553,9 +544,6 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -579,7 +567,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -595,38 +582,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -893,9 +890,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1011,88 +1008,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>53</v>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
+      <c r="A3" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1111,12 +1108,10 @@
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>5</v>
+      <c r="A4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1135,12 +1130,10 @@
       <c r="R4" s="6"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="27"/>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="A5" s="29"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -1159,12 +1152,12 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>4</v>
+      <c r="A6" s="29"/>
+      <c r="B6" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1183,12 +1176,10 @@
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>5</v>
+      <c r="A7" s="29"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -1207,12 +1198,10 @@
       <c r="R7" s="6"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>6</v>
+      <c r="A8" s="30"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -1231,14 +1220,14 @@
       <c r="R8" s="4"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
+      <c r="A9" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1257,12 +1246,10 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>5</v>
+      <c r="A10" s="29"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -1281,12 +1268,10 @@
       <c r="R10" s="6"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A11" s="29"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -1305,12 +1290,12 @@
       <c r="R11" s="4"/>
     </row>
     <row r="12" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
+      <c r="A12" s="29"/>
+      <c r="B12" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1329,12 +1314,10 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="27"/>
-      <c r="B13" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>5</v>
+      <c r="A13" s="29"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -1353,12 +1336,10 @@
       <c r="R13" s="6"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="A14" s="29"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -1377,12 +1358,12 @@
       <c r="R14" s="4"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
+      <c r="A15" s="29"/>
+      <c r="B15" s="25" t="s">
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -1401,12 +1382,10 @@
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>5</v>
+      <c r="A16" s="29"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1425,12 +1404,10 @@
       <c r="R16" s="6"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="A17" s="29"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -1449,12 +1426,12 @@
       <c r="R17" s="4"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
+      <c r="A18" s="29"/>
+      <c r="B18" s="25" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1473,12 +1450,10 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>5</v>
+      <c r="A19" s="29"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -1497,12 +1472,10 @@
       <c r="R19" s="6"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="B20" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A20" s="29"/>
+      <c r="B20" s="27"/>
       <c r="C20" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -1521,12 +1494,12 @@
       <c r="R20" s="4"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="B21" s="1" t="s">
-        <v>13</v>
+      <c r="A21" s="29"/>
+      <c r="B21" s="25" t="s">
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1545,12 +1518,10 @@
       <c r="R21" s="2"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
-      <c r="B22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>5</v>
+      <c r="A22" s="29"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -1569,12 +1540,10 @@
       <c r="R22" s="6"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
-      <c r="B23" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A23" s="29"/>
+      <c r="B23" s="27"/>
       <c r="C23" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -1593,12 +1562,12 @@
       <c r="R23" s="4"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="B24" s="1" t="s">
-        <v>14</v>
+      <c r="A24" s="29"/>
+      <c r="B24" s="25" t="s">
+        <v>29</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1617,12 +1586,10 @@
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="B25" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>5</v>
+      <c r="A25" s="29"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -1641,12 +1608,10 @@
       <c r="R25" s="6"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="B26" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A26" s="29"/>
+      <c r="B26" s="27"/>
       <c r="C26" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -1665,12 +1630,12 @@
       <c r="R26" s="4"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
-      <c r="B27" s="1" t="s">
-        <v>15</v>
+      <c r="A27" s="29"/>
+      <c r="B27" s="25" t="s">
+        <v>30</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -1689,12 +1654,10 @@
       <c r="R27" s="2"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="27"/>
-      <c r="B28" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>5</v>
+      <c r="A28" s="29"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -1713,12 +1676,10 @@
       <c r="R28" s="6"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="A29" s="33"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -1737,14 +1698,14 @@
       <c r="R29" s="4"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
+      <c r="A30" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>32</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1763,12 +1724,10 @@
       <c r="R30" s="2"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="B31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>5</v>
+      <c r="A31" s="29"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -1787,12 +1746,10 @@
       <c r="R31" s="6"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="B32" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="A32" s="29"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1811,12 +1768,12 @@
       <c r="R32" s="4"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="B33" s="1" t="s">
-        <v>18</v>
+      <c r="A33" s="29"/>
+      <c r="B33" s="25" t="s">
+        <v>33</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -1835,12 +1792,10 @@
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="27"/>
-      <c r="B34" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>5</v>
+      <c r="A34" s="29"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -1859,12 +1814,10 @@
       <c r="R34" s="6"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="27"/>
-      <c r="B35" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="A35" s="29"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -1883,12 +1836,12 @@
       <c r="R35" s="4"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="27"/>
-      <c r="B36" s="1" t="s">
+      <c r="A36" s="29"/>
+      <c r="B36" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -1907,12 +1860,10 @@
       <c r="R36" s="2"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="B37" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>5</v>
+      <c r="A37" s="29"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -1931,12 +1882,10 @@
       <c r="R37" s="6"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="27"/>
-      <c r="B38" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A38" s="29"/>
+      <c r="B38" s="27"/>
       <c r="C38" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -1955,12 +1904,12 @@
       <c r="R38" s="4"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="27"/>
-      <c r="B39" s="1" t="s">
-        <v>20</v>
+      <c r="A39" s="29"/>
+      <c r="B39" s="25" t="s">
+        <v>35</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -1979,12 +1928,10 @@
       <c r="R39" s="2"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="B40" s="8" t="s">
+      <c r="A40" s="29"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>5</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -2003,12 +1950,10 @@
       <c r="R40" s="6"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="B41" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A41" s="29"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2027,12 +1972,12 @@
       <c r="R41" s="4"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="B42" s="1" t="s">
-        <v>21</v>
+      <c r="A42" s="29"/>
+      <c r="B42" s="25" t="s">
+        <v>36</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -2051,12 +1996,10 @@
       <c r="R42" s="2"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
-      <c r="B43" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>5</v>
+      <c r="A43" s="29"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -2075,12 +2018,10 @@
       <c r="R43" s="6"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="29"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -2099,12 +2040,12 @@
       <c r="R44" s="4"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="1" t="s">
-        <v>22</v>
+      <c r="A45" s="29"/>
+      <c r="B45" s="25" t="s">
+        <v>37</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -2123,12 +2064,10 @@
       <c r="R45" s="2"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
-      <c r="B46" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>5</v>
+      <c r="A46" s="29"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -2147,12 +2086,10 @@
       <c r="R46" s="6"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="27"/>
-      <c r="B47" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="A47" s="29"/>
+      <c r="B47" s="27"/>
       <c r="C47" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -2171,12 +2108,12 @@
       <c r="R47" s="4"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="B48" s="1" t="s">
-        <v>23</v>
+      <c r="A48" s="29"/>
+      <c r="B48" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -2195,12 +2132,10 @@
       <c r="R48" s="2"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>5</v>
+      <c r="A49" s="29"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -2219,12 +2154,10 @@
       <c r="R49" s="6"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="A50" s="29"/>
+      <c r="B50" s="27"/>
       <c r="C50" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -2243,12 +2176,12 @@
       <c r="R50" s="4"/>
     </row>
     <row r="51" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="1" t="s">
-        <v>24</v>
+      <c r="A51" s="29"/>
+      <c r="B51" s="25" t="s">
+        <v>39</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -2267,12 +2200,10 @@
       <c r="R51" s="2"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="27"/>
-      <c r="B52" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>5</v>
+      <c r="A52" s="29"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -2291,12 +2222,10 @@
       <c r="R52" s="6"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="27"/>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A53" s="29"/>
+      <c r="B53" s="27"/>
       <c r="C53" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -2315,12 +2244,12 @@
       <c r="R53" s="4"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="27"/>
-      <c r="B54" s="1" t="s">
-        <v>25</v>
+      <c r="A54" s="29"/>
+      <c r="B54" s="25" t="s">
+        <v>40</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -2339,12 +2268,10 @@
       <c r="R54" s="2"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="27"/>
-      <c r="B55" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>5</v>
+      <c r="A55" s="29"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -2363,12 +2290,10 @@
       <c r="R55" s="6"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="27"/>
-      <c r="B56" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A56" s="29"/>
+      <c r="B56" s="27"/>
       <c r="C56" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -2387,12 +2312,12 @@
       <c r="R56" s="4"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="27"/>
-      <c r="B57" s="1" t="s">
-        <v>26</v>
+      <c r="A57" s="29"/>
+      <c r="B57" s="25" t="s">
+        <v>41</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -2411,12 +2336,10 @@
       <c r="R57" s="2"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="27"/>
-      <c r="B58" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>5</v>
+      <c r="A58" s="29"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -2435,12 +2358,10 @@
       <c r="R58" s="6"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="28"/>
-      <c r="B59" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="A59" s="33"/>
+      <c r="B59" s="27"/>
       <c r="C59" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -2459,14 +2380,14 @@
       <c r="R59" s="4"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>28</v>
+      <c r="A60" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>43</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -2485,12 +2406,10 @@
       <c r="R60" s="2"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A61" s="27"/>
-      <c r="B61" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>5</v>
+      <c r="A61" s="29"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -2509,12 +2428,10 @@
       <c r="R61" s="6"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="27"/>
-      <c r="B62" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="A62" s="29"/>
+      <c r="B62" s="27"/>
       <c r="C62" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -2533,12 +2450,12 @@
       <c r="R62" s="4"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="27"/>
-      <c r="B63" s="1" t="s">
-        <v>29</v>
+      <c r="A63" s="29"/>
+      <c r="B63" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -2557,12 +2474,10 @@
       <c r="R63" s="2"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="27"/>
-      <c r="B64" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>5</v>
+      <c r="A64" s="29"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -2581,12 +2496,10 @@
       <c r="R64" s="6"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="27"/>
-      <c r="B65" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A65" s="29"/>
+      <c r="B65" s="27"/>
       <c r="C65" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -2605,12 +2518,12 @@
       <c r="R65" s="4"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="27"/>
-      <c r="B66" s="1" t="s">
-        <v>30</v>
+      <c r="A66" s="29"/>
+      <c r="B66" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -2629,12 +2542,10 @@
       <c r="R66" s="2"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="27"/>
-      <c r="B67" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>5</v>
+      <c r="A67" s="29"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -2653,12 +2564,10 @@
       <c r="R67" s="6"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="27"/>
-      <c r="B68" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A68" s="29"/>
+      <c r="B68" s="27"/>
       <c r="C68" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -2677,12 +2586,12 @@
       <c r="R68" s="4"/>
     </row>
     <row r="69" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="27"/>
-      <c r="B69" s="1" t="s">
-        <v>31</v>
+      <c r="A69" s="29"/>
+      <c r="B69" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -2701,12 +2610,10 @@
       <c r="R69" s="2"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A70" s="27"/>
-      <c r="B70" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>5</v>
+      <c r="A70" s="29"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -2725,12 +2632,10 @@
       <c r="R70" s="6"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="27"/>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A71" s="29"/>
+      <c r="B71" s="27"/>
       <c r="C71" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -2749,12 +2654,12 @@
       <c r="R71" s="4"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="27"/>
-      <c r="B72" s="1" t="s">
-        <v>32</v>
+      <c r="A72" s="29"/>
+      <c r="B72" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -2773,12 +2678,10 @@
       <c r="R72" s="2"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="27"/>
-      <c r="B73" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>5</v>
+      <c r="A73" s="29"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -2797,12 +2700,10 @@
       <c r="R73" s="6"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A74" s="27"/>
-      <c r="B74" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A74" s="29"/>
+      <c r="B74" s="27"/>
       <c r="C74" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -2821,12 +2722,12 @@
       <c r="R74" s="4"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A75" s="27"/>
-      <c r="B75" s="1" t="s">
-        <v>33</v>
+      <c r="A75" s="29"/>
+      <c r="B75" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -2845,12 +2746,10 @@
       <c r="R75" s="2"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A76" s="27"/>
-      <c r="B76" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>5</v>
+      <c r="A76" s="29"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -2869,12 +2768,10 @@
       <c r="R76" s="6"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A77" s="27"/>
-      <c r="B77" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="A77" s="29"/>
+      <c r="B77" s="27"/>
       <c r="C77" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -2893,12 +2790,12 @@
       <c r="R77" s="4"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" s="27"/>
-      <c r="B78" s="1" t="s">
-        <v>34</v>
+      <c r="A78" s="29"/>
+      <c r="B78" s="25" t="s">
+        <v>49</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -2917,12 +2814,10 @@
       <c r="R78" s="2"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A79" s="27"/>
-      <c r="B79" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>5</v>
+      <c r="A79" s="29"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
@@ -2941,12 +2836,10 @@
       <c r="R79" s="6"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A80" s="27"/>
-      <c r="B80" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A80" s="29"/>
+      <c r="B80" s="27"/>
       <c r="C80" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -2965,12 +2858,12 @@
       <c r="R80" s="4"/>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A81" s="27"/>
-      <c r="B81" s="1" t="s">
-        <v>35</v>
+      <c r="A81" s="29"/>
+      <c r="B81" s="25" t="s">
+        <v>50</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -2989,12 +2882,10 @@
       <c r="R81" s="2"/>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A82" s="27"/>
-      <c r="B82" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>5</v>
+      <c r="A82" s="29"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -3013,12 +2904,10 @@
       <c r="R82" s="6"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A83" s="27"/>
-      <c r="B83" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="A83" s="29"/>
+      <c r="B83" s="27"/>
       <c r="C83" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -3037,12 +2926,12 @@
       <c r="R83" s="4"/>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A84" s="27"/>
-      <c r="B84" s="1" t="s">
-        <v>36</v>
+      <c r="A84" s="29"/>
+      <c r="B84" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
@@ -3061,12 +2950,10 @@
       <c r="R84" s="2"/>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A85" s="27"/>
-      <c r="B85" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>5</v>
+      <c r="A85" s="29"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
@@ -3085,12 +2972,10 @@
       <c r="R85" s="6"/>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A86" s="27"/>
-      <c r="B86" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="A86" s="29"/>
+      <c r="B86" s="27"/>
       <c r="C86" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -3109,12 +2994,12 @@
       <c r="R86" s="4"/>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A87" s="27"/>
-      <c r="B87" s="1" t="s">
-        <v>37</v>
+      <c r="A87" s="29"/>
+      <c r="B87" s="25" t="s">
+        <v>52</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
@@ -3133,12 +3018,10 @@
       <c r="R87" s="2"/>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A88" s="27"/>
-      <c r="B88" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>5</v>
+      <c r="A88" s="29"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -3157,12 +3040,10 @@
       <c r="R88" s="6"/>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A89" s="27"/>
-      <c r="B89" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="A89" s="29"/>
+      <c r="B89" s="27"/>
       <c r="C89" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -3181,12 +3062,12 @@
       <c r="R89" s="4"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A90" s="27"/>
-      <c r="B90" s="1" t="s">
-        <v>38</v>
+      <c r="A90" s="29"/>
+      <c r="B90" s="25" t="s">
+        <v>53</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -3205,12 +3086,10 @@
       <c r="R90" s="2"/>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A91" s="27"/>
-      <c r="B91" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>5</v>
+      <c r="A91" s="29"/>
+      <c r="B91" s="26"/>
+      <c r="C91" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
@@ -3229,12 +3108,10 @@
       <c r="R91" s="6"/>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A92" s="28"/>
-      <c r="B92" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="A92" s="33"/>
+      <c r="B92" s="27"/>
       <c r="C92" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -3253,58 +3130,73 @@
       <c r="R92" s="4"/>
     </row>
     <row r="93" spans="1:18" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="B93" s="32"/>
-      <c r="C93" s="32"/>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="33"/>
-      <c r="G93" s="33"/>
-      <c r="H93" s="33"/>
-      <c r="I93" s="33"/>
-      <c r="J93" s="33"/>
-      <c r="K93" s="33"/>
-      <c r="L93" s="33"/>
-      <c r="M93" s="33"/>
-      <c r="N93" s="33"/>
-      <c r="O93" s="33"/>
-      <c r="P93" s="33"/>
-      <c r="Q93" s="33"/>
-      <c r="R93" s="33"/>
+      <c r="A93" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B93" s="25"/>
+      <c r="C93" s="25"/>
     </row>
     <row r="94" spans="1:18" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="B94" s="35"/>
-      <c r="C94" s="35"/>
-      <c r="D94" s="36"/>
-      <c r="E94" s="36"/>
-      <c r="F94" s="36"/>
-      <c r="G94" s="36"/>
-      <c r="H94" s="36"/>
-      <c r="I94" s="36"/>
-      <c r="J94" s="36"/>
-      <c r="K94" s="36"/>
-      <c r="L94" s="36"/>
-      <c r="M94" s="36"/>
-      <c r="N94" s="36"/>
-      <c r="O94" s="36"/>
-      <c r="P94" s="36"/>
-      <c r="Q94" s="36"/>
-      <c r="R94" s="36"/>
+      <c r="A94" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="24"/>
+      <c r="K94" s="24"/>
+      <c r="L94" s="24"/>
+      <c r="M94" s="24"/>
+      <c r="N94" s="24"/>
+      <c r="O94" s="24"/>
+      <c r="P94" s="24"/>
+      <c r="Q94" s="24"/>
+      <c r="R94" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="37">
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A94:C94"/>
     <mergeCell ref="A93:C93"/>
     <mergeCell ref="A60:A92"/>
     <mergeCell ref="A30:A59"/>
-    <mergeCell ref="A3:A5"/>
     <mergeCell ref="A9:A29"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B87:B89"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B51:B53"/>
   </mergeCells>
   <conditionalFormatting sqref="D3:R3">
     <cfRule type="top10" dxfId="33" priority="60" bottom="1" rank="1"/>
@@ -3411,74 +3303,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="A1" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="O2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="N2" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>3</v>
+      <c r="A3" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3493,11 +3385,11 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="11"/>
+      <c r="O3" s="10"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>7</v>
+      <c r="A4" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -3512,11 +3404,11 @@
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
-      <c r="O4" s="13"/>
+      <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>9</v>
+      <c r="A5" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -3531,11 +3423,11 @@
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="13"/>
+      <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>10</v>
+      <c r="A6" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -3550,11 +3442,11 @@
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="13"/>
+      <c r="O6" s="12"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>11</v>
+      <c r="A7" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3569,11 +3461,11 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="13"/>
+      <c r="O7" s="12"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>12</v>
+      <c r="A8" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -3588,11 +3480,11 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="12"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>13</v>
+      <c r="A9" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3607,11 +3499,11 @@
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="12"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>14</v>
+      <c r="A10" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -3626,11 +3518,11 @@
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
-      <c r="O10" s="13"/>
+      <c r="O10" s="12"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>15</v>
+      <c r="A11" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3645,11 +3537,11 @@
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="13"/>
+      <c r="O11" s="12"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>17</v>
+      <c r="A12" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -3664,11 +3556,11 @@
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
-      <c r="O12" s="13"/>
+      <c r="O12" s="12"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>18</v>
+      <c r="A13" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -3683,11 +3575,11 @@
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
-      <c r="O13" s="13"/>
+      <c r="O13" s="12"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>19</v>
+      <c r="A14" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3702,11 +3594,11 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
-      <c r="O14" s="13"/>
+      <c r="O14" s="12"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>20</v>
+      <c r="A15" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -3721,11 +3613,11 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="12"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>21</v>
+      <c r="A16" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -3740,11 +3632,11 @@
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
-      <c r="O16" s="13"/>
+      <c r="O16" s="12"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>22</v>
+      <c r="A17" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3759,11 +3651,11 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
-      <c r="O17" s="13"/>
+      <c r="O17" s="12"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>23</v>
+      <c r="A18" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3778,11 +3670,11 @@
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="13"/>
+      <c r="O18" s="12"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>24</v>
+      <c r="A19" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -3797,11 +3689,11 @@
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
-      <c r="O19" s="13"/>
+      <c r="O19" s="12"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>25</v>
+      <c r="A20" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3816,11 +3708,11 @@
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
-      <c r="O20" s="13"/>
+      <c r="O20" s="12"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>26</v>
+      <c r="A21" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -3835,11 +3727,11 @@
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
-      <c r="O21" s="13"/>
+      <c r="O21" s="12"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>28</v>
+      <c r="A22" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -3854,11 +3746,11 @@
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
-      <c r="O22" s="13"/>
+      <c r="O22" s="12"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>29</v>
+      <c r="A23" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -3873,11 +3765,11 @@
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
-      <c r="O23" s="13"/>
+      <c r="O23" s="12"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>30</v>
+      <c r="A24" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3892,11 +3784,11 @@
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
-      <c r="O24" s="13"/>
+      <c r="O24" s="12"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>31</v>
+      <c r="A25" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -3911,11 +3803,11 @@
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
-      <c r="O25" s="13"/>
+      <c r="O25" s="12"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>32</v>
+      <c r="A26" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -3930,11 +3822,11 @@
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
-      <c r="O26" s="13"/>
+      <c r="O26" s="12"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>33</v>
+      <c r="A27" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -3949,11 +3841,11 @@
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
-      <c r="O27" s="13"/>
+      <c r="O27" s="12"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>34</v>
+      <c r="A28" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -3968,11 +3860,11 @@
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
-      <c r="O28" s="13"/>
+      <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>35</v>
+      <c r="A29" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -3987,11 +3879,11 @@
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
-      <c r="O29" s="13"/>
+      <c r="O29" s="12"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>36</v>
+      <c r="A30" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4006,11 +3898,11 @@
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
-      <c r="O30" s="13"/>
+      <c r="O30" s="12"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>37</v>
+      <c r="A31" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4025,26 +3917,26 @@
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
-      <c r="O31" s="13"/>
+      <c r="O31" s="12"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="10"/>
+      <c r="A32" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4070,640 +3962,640 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="A1" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="O2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="N2" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
+      <c r="A3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="A4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
+      <c r="A5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
+      <c r="A6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
+      <c r="A7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
+      <c r="A8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
+      <c r="A9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
+      <c r="A10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
+      <c r="A11" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
+      <c r="A12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
+      <c r="A13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
+      <c r="A14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
+      <c r="A15" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
+      <c r="A16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
+      <c r="A17" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
+      <c r="A18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
+      <c r="A19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
+      <c r="A20" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
+      <c r="A21" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
+      <c r="A22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
+      <c r="A23" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
+      <c r="A24" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
+      <c r="A25" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
+      <c r="A26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
+      <c r="A27" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
+      <c r="A28" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
+      <c r="A29" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
+      <c r="A30" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
+      <c r="A31" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
+      <c r="A32" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4729,74 +4621,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="A1" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="O2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="N2" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>3</v>
+      <c r="A3" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4814,8 +4706,8 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>7</v>
+      <c r="A4" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -4833,8 +4725,8 @@
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>9</v>
+      <c r="A5" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -4852,8 +4744,8 @@
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>10</v>
+      <c r="A6" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -4871,8 +4763,8 @@
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>11</v>
+      <c r="A7" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4890,8 +4782,8 @@
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>12</v>
+      <c r="A8" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -4909,8 +4801,8 @@
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>13</v>
+      <c r="A9" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4928,8 +4820,8 @@
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>14</v>
+      <c r="A10" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -4947,8 +4839,8 @@
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>15</v>
+      <c r="A11" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4966,8 +4858,8 @@
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>17</v>
+      <c r="A12" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -4985,8 +4877,8 @@
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>18</v>
+      <c r="A13" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -5004,8 +4896,8 @@
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>19</v>
+      <c r="A14" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -5023,8 +4915,8 @@
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>20</v>
+      <c r="A15" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -5042,8 +4934,8 @@
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>21</v>
+      <c r="A16" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -5061,8 +4953,8 @@
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>22</v>
+      <c r="A17" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -5080,8 +4972,8 @@
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>23</v>
+      <c r="A18" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -5099,8 +4991,8 @@
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>24</v>
+      <c r="A19" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -5118,8 +5010,8 @@
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>25</v>
+      <c r="A20" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -5137,8 +5029,8 @@
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>26</v>
+      <c r="A21" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -5156,8 +5048,8 @@
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>28</v>
+      <c r="A22" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -5175,8 +5067,8 @@
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>29</v>
+      <c r="A23" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -5194,8 +5086,8 @@
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>30</v>
+      <c r="A24" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -5213,8 +5105,8 @@
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>31</v>
+      <c r="A25" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -5232,8 +5124,8 @@
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>32</v>
+      <c r="A26" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -5251,8 +5143,8 @@
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>33</v>
+      <c r="A27" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -5270,8 +5162,8 @@
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>34</v>
+      <c r="A28" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -5289,8 +5181,8 @@
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>35</v>
+      <c r="A29" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -5308,8 +5200,8 @@
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>36</v>
+      <c r="A30" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -5327,8 +5219,8 @@
       <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>37</v>
+      <c r="A31" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -5346,23 +5238,23 @@
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="A32" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5388,640 +5280,640 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="A1" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="O2" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
+        <v>18</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="A4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
+      <c r="A5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
+      <c r="A6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
+      <c r="A7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
+      <c r="A8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
+      <c r="A9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
+      <c r="A10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
+      <c r="A11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
+      <c r="A12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
+      <c r="A13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
+      <c r="A14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
+      <c r="A15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
+      <c r="A16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
+      <c r="A17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
+      <c r="A18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
+      <c r="A19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
+      <c r="A20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
+      <c r="A21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
+      <c r="A22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
+      <c r="A23" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
+      <c r="A24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
+      <c r="A25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
+      <c r="A26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
+      <c r="A27" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
+      <c r="A28" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
+      <c r="A29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
+      <c r="A30" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
+      <c r="A31" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
+        <v>53</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6047,74 +5939,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="A1" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="O2" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6132,540 +6024,540 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
+      <c r="A5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
+      <c r="A11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
+      <c r="A12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
+      <c r="A13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
+      <c r="A14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
+      <c r="A15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
+      <c r="A16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
+      <c r="A17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
+      <c r="A18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
+      <c r="A19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
+      <c r="A20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
+      <c r="A21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
+      <c r="A22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
+      <c r="A23" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
+      <c r="A24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
+      <c r="A25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
+      <c r="A26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
+      <c r="A27" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
+      <c r="A28" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
+      <c r="A29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
+      <c r="A30" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
+      <c r="A31" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -6695,1079 +6587,1084 @@
   <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="D2" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="E2" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="F2" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="G2" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="H2" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="I2" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="J2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="K2" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="L2" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="M2" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="N2" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="O2" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="P2" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="Q2" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="R2" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="S2" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="R2" s="17" t="s">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="16"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="21"/>
-      <c r="R37" s="21"/>
-      <c r="S37" s="21"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="16"/>
+      <c r="R39" s="16"/>
+      <c r="S39" s="16"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16"/>
+      <c r="S40" s="16"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="16"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="16"/>
+      <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16"/>
+      <c r="S41" s="16"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="B42" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="C42" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16"/>
+      <c r="Q42" s="16"/>
+      <c r="R42" s="16"/>
+      <c r="S42" s="16"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="16"/>
+      <c r="O43" s="16"/>
+      <c r="P43" s="16"/>
+      <c r="Q43" s="16"/>
+      <c r="R43" s="16"/>
+      <c r="S43" s="16"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
+      <c r="A44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="16"/>
+      <c r="Q44" s="16"/>
+      <c r="R44" s="16"/>
+      <c r="S44" s="16"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7782,75 +7679,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="23" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="23" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="23" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="23" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="23" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="23" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="23" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="23" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>118</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
